--- a/src/main/resources/static/PreviousGroups.xlsx
+++ b/src/main/resources/static/PreviousGroups.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14Z90N\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14Z90N\Desktop\coding\WorkSpace\GroupAssignerAssist\src\main\resources\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785C59D3-A63A-472A-A207-75B413E50E99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12A5014-8B3A-4DB7-ADF7-BC4300788F95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Group</t>
   </si>
@@ -28,51 +28,123 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AAA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BBB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DDD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EEE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FFF</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Module1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Module2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>김지연</t>
   </si>
   <si>
-    <t>Module3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>안동석</t>
   </si>
   <si>
-    <t>Module4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>오성민</t>
+  </si>
+  <si>
+    <t>정우석</t>
+  </si>
+  <si>
+    <t>김명한</t>
+  </si>
+  <si>
+    <t>김아람</t>
+  </si>
+  <si>
+    <t>김영민</t>
+  </si>
+  <si>
+    <t>노성은</t>
+  </si>
+  <si>
+    <t>김미라</t>
+  </si>
+  <si>
+    <t>김수근</t>
+  </si>
+  <si>
+    <t>정윤식</t>
+  </si>
+  <si>
+    <t>최성민</t>
+  </si>
+  <si>
+    <t>배지현</t>
+  </si>
+  <si>
+    <t>송하준</t>
+  </si>
+  <si>
+    <t>유현주</t>
+  </si>
+  <si>
+    <t>이현우</t>
+  </si>
+  <si>
+    <t>김경호</t>
+  </si>
+  <si>
+    <t>김희정</t>
+  </si>
+  <si>
+    <t>조남중</t>
+  </si>
+  <si>
+    <t>최채석</t>
+  </si>
+  <si>
+    <t>김윤희</t>
+  </si>
+  <si>
+    <t>서정철</t>
+  </si>
+  <si>
+    <t>정원용</t>
+  </si>
+  <si>
+    <t>한소영</t>
+  </si>
+  <si>
+    <t>신지영</t>
+  </si>
+  <si>
+    <t>안상미</t>
+  </si>
+  <si>
+    <t>전한수</t>
+  </si>
+  <si>
+    <t>최용은</t>
+  </si>
+  <si>
+    <t>구광민</t>
+  </si>
+  <si>
+    <t>김민호</t>
+  </si>
+  <si>
+    <t>이진영</t>
+  </si>
+  <si>
+    <t>최혜윤</t>
+  </si>
+  <si>
+    <t>오남훈</t>
+  </si>
+  <si>
+    <t>이유정</t>
+  </si>
+  <si>
+    <t>이종훈</t>
+  </si>
+  <si>
+    <t>전진우</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -85,6 +157,7 @@
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -100,8 +173,33 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,8 +217,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -169,27 +273,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -197,11 +347,2437 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 4 2" xfId="1" xr:uid="{20B4B6DB-7E03-4CD3-A56A-D37BE0E7A5CF}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="249">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -511,217 +3087,911 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="6"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="B4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="6" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B7" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
         <v>2</v>
       </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>2</v>
       </c>
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="11" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>3</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>4</v>
       </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="B15" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>4</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>4</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
         <v>5</v>
       </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="B19" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
         <v>6</v>
       </c>
+      <c r="B23" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>3</v>
+    <row r="24" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>6</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="s">
+    <row r="25" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
         <v>6</v>
       </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="B25" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A26" s="10">
+        <v>6</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
         <v>7</v>
       </c>
-      <c r="G6" s="4">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="B27" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="4">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
+    <row r="28" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>7</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="29" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
         <v>7</v>
       </c>
-      <c r="C8" s="4">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B29" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A30" s="10">
         <v>7</v>
       </c>
-      <c r="E8" s="4">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="4">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>7</v>
+      <c r="B30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>8</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>8</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>8</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A34" s="10">
+        <v>8</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>9</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A36" s="9">
+        <v>9</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A37" s="9">
+        <v>9</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="10">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B17:B21 B3 B9:B14 B26:B38">
+    <cfRule type="cellIs" dxfId="248" priority="73" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" dxfId="247" priority="72" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" dxfId="246" priority="71" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12 B14">
+    <cfRule type="cellIs" dxfId="245" priority="70" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" dxfId="244" priority="69" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" dxfId="243" priority="68" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" dxfId="242" priority="67" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="cellIs" dxfId="241" priority="66" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="cellIs" dxfId="240" priority="65" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="cellIs" dxfId="239" priority="64" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="cellIs" dxfId="238" priority="63" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B8">
+    <cfRule type="cellIs" dxfId="237" priority="62" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:B31">
+    <cfRule type="cellIs" dxfId="236" priority="61" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="cellIs" dxfId="235" priority="60" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:B30">
+    <cfRule type="cellIs" dxfId="234" priority="59" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="cellIs" dxfId="233" priority="58" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="cellIs" dxfId="232" priority="57" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" dxfId="231" priority="56" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" dxfId="230" priority="55" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" dxfId="229" priority="54" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="cellIs" dxfId="228" priority="53" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="cellIs" dxfId="227" priority="52" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32:B38">
+    <cfRule type="cellIs" dxfId="226" priority="51" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B38">
+    <cfRule type="cellIs" dxfId="225" priority="50" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="224" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="223" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="219" priority="79" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="218" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="217" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="213" priority="85" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="duplicateValues" dxfId="212" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="duplicateValues" dxfId="211" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="duplicateValues" dxfId="210" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="206" priority="92" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="205" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13 B9:B10">
+    <cfRule type="duplicateValues" dxfId="204" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B14 B9:B10">
+    <cfRule type="duplicateValues" dxfId="203" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B14 B9:B10">
+    <cfRule type="duplicateValues" dxfId="202" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13 B9:B10">
+    <cfRule type="duplicateValues" dxfId="198" priority="100" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B14 B9:B10">
+    <cfRule type="duplicateValues" dxfId="197" priority="101" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="196" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="192" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="191" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="187" priority="111" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="186" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="185" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="181" priority="117" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B13">
+    <cfRule type="duplicateValues" dxfId="180" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B13">
+    <cfRule type="duplicateValues" dxfId="179" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B13">
+    <cfRule type="duplicateValues" dxfId="175" priority="123" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="duplicateValues" dxfId="174" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="duplicateValues" dxfId="173" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="duplicateValues" dxfId="169" priority="129" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="168" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="167" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="163" priority="135" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="duplicateValues" dxfId="162" priority="136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="duplicateValues" dxfId="161" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="140"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="duplicateValues" dxfId="157" priority="141" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B8">
+    <cfRule type="duplicateValues" dxfId="156" priority="142"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B8">
+    <cfRule type="duplicateValues" dxfId="155" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B8">
+    <cfRule type="duplicateValues" dxfId="151" priority="147" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:B20">
+    <cfRule type="duplicateValues" dxfId="150" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:B20">
+    <cfRule type="duplicateValues" dxfId="149" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:B20">
+    <cfRule type="duplicateValues" dxfId="145" priority="153" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="144" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="143" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="158"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="139" priority="159" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="138" priority="160"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="137" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="133" priority="165" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="132" priority="166"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B26">
+    <cfRule type="duplicateValues" dxfId="131" priority="167"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B26">
+    <cfRule type="duplicateValues" dxfId="130" priority="168" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:B30">
+    <cfRule type="duplicateValues" dxfId="129" priority="169"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:B30">
+    <cfRule type="duplicateValues" dxfId="128" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="173"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:B30">
+    <cfRule type="duplicateValues" dxfId="124" priority="174" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="123" priority="175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="122" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="179"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="118" priority="180" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="117" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="116" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="185"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="112" priority="186" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="111" priority="187"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="110" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="191"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="106" priority="192" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="105" priority="193"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="104" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="197"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="100" priority="198" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="99" priority="199"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="98" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="94" priority="204" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="93" priority="205"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="92" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="209"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="88" priority="210" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="87" priority="211"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="86" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="215"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="82" priority="216" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B38">
+    <cfRule type="duplicateValues" dxfId="81" priority="217"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B38">
+    <cfRule type="duplicateValues" dxfId="80" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="221"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B38">
+    <cfRule type="duplicateValues" dxfId="76" priority="222" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="75" priority="223"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="74" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="227"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="70" priority="228" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32:B38">
+    <cfRule type="duplicateValues" dxfId="69" priority="229"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="68" priority="230"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="67" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="234"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="63" priority="235" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B20">
+    <cfRule type="duplicateValues" dxfId="62" priority="236"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B20">
+    <cfRule type="duplicateValues" dxfId="61" priority="237"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="60" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="59" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="55" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="54" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="53" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="49" priority="36" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="48" priority="37" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="42" priority="43" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="36" priority="49" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="cellIs" dxfId="35" priority="18" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="34" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="29" priority="24" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" dxfId="28" priority="11" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="27" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="22" priority="17" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="21" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="241"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="17" priority="242"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B26">
+    <cfRule type="duplicateValues" dxfId="16" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="246"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="12" priority="247" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:B31">
+    <cfRule type="duplicateValues" dxfId="11" priority="248"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:B31">
+    <cfRule type="duplicateValues" dxfId="10" priority="249"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="cellIs" dxfId="9" priority="3" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="cellIs" dxfId="8" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="cellIs" dxfId="7" priority="1" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="duplicateValues" dxfId="1" priority="9" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
